--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kashi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User-PC\Documents\Mutual_Fund_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{516F7660-90FF-475F-8C53-4D044B14E9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8191B72F-13AA-4747-BA3E-79DDF4797B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1725" yWindow="1920" windowWidth="18000" windowHeight="9000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1598,22 +1598,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J167"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" style="2" customWidth="1"/>
     <col min="2" max="2" width="35" style="2" customWidth="1"/>
     <col min="3" max="3" width="61" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="2"/>
-    <col min="5" max="5" width="14.5546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="2"/>
+    <col min="5" max="5" width="14.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="2" customWidth="1"/>
     <col min="8" max="8" width="12" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.109375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="14.109375" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="2"/>
+    <col min="9" max="9" width="12.140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>375</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>34</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>37</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>41</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>41</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>46</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>46</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>51</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>54</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>56</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>56</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>56</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>59</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>0.13700000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>59</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>59</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>59</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>59</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>59</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>66</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>68</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>68</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>73</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>73</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>68</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>68</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>73</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>73</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>41</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>68</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>68</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>73</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>73</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>41</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>68</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>68</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>102</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>102</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>102</v>
       </c>
@@ -3469,7 +3469,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>110</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>110</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>110</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>110</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>110</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>110</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>110</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>123</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>123</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>123</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>130</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>133</v>
       </c>
@@ -3853,7 +3853,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>136</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>136</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>136</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>136</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>145</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>148</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>151</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>151</v>
       </c>
@@ -4109,7 +4109,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>151</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>151</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>151</v>
       </c>
@@ -4205,7 +4205,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>151</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>151</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>151</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>151</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>169</v>
       </c>
@@ -4365,7 +4365,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>169</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>174</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>174</v>
       </c>
@@ -4461,7 +4461,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>174</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>181</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>184</v>
       </c>
@@ -4557,7 +4557,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>184</v>
       </c>
@@ -4589,7 +4589,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>184</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>184</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>184</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>195</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>195</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>195</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>195</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>195</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>195</v>
       </c>
@@ -4877,7 +4877,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>195</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>208</v>
       </c>
@@ -4941,7 +4941,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>208</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>208</v>
       </c>
@@ -5005,7 +5005,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>215</v>
       </c>
@@ -5037,7 +5037,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>215</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>220</v>
       </c>
@@ -5101,7 +5101,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>220</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>208</v>
       </c>
@@ -5165,7 +5165,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>215</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>220</v>
       </c>
@@ -5229,7 +5229,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>220</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>208</v>
       </c>
@@ -5293,7 +5293,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>208</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>215</v>
       </c>
@@ -5357,7 +5357,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>220</v>
       </c>
@@ -5389,7 +5389,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>220</v>
       </c>
@@ -5421,7 +5421,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>215</v>
       </c>
@@ -5453,7 +5453,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>215</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>220</v>
       </c>
@@ -5517,7 +5517,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>215</v>
       </c>
@@ -5549,7 +5549,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>220</v>
       </c>
@@ -5581,7 +5581,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>252</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>252</v>
       </c>
@@ -5645,7 +5645,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>252</v>
       </c>
@@ -5677,7 +5677,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>252</v>
       </c>
@@ -5709,7 +5709,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>291</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>291</v>
       </c>
@@ -5773,7 +5773,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>291</v>
       </c>
@@ -5805,7 +5805,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>291</v>
       </c>
@@ -5837,7 +5837,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>291</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>291</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>304</v>
       </c>
@@ -5933,7 +5933,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>304</v>
       </c>
@@ -5965,7 +5965,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>304</v>
       </c>
@@ -5997,7 +5997,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>304</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>305</v>
       </c>
@@ -6061,7 +6061,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>305</v>
       </c>
@@ -6093,7 +6093,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>305</v>
       </c>
@@ -6125,7 +6125,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>306</v>
       </c>
@@ -6157,7 +6157,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>326</v>
       </c>
@@ -6189,7 +6189,7 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>326</v>
       </c>
@@ -6221,7 +6221,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>326</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>326</v>
       </c>
@@ -6285,7 +6285,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>333</v>
       </c>
@@ -6317,7 +6317,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>333</v>
       </c>
@@ -6349,7 +6349,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>333</v>
       </c>
@@ -6381,7 +6381,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>333</v>
       </c>
@@ -6413,7 +6413,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>333</v>
       </c>
@@ -6445,7 +6445,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>334</v>
       </c>
@@ -6477,7 +6477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>334</v>
       </c>
@@ -6509,7 +6509,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>334</v>
       </c>
@@ -6541,7 +6541,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>334</v>
       </c>
@@ -6573,7 +6573,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>334</v>
       </c>
@@ -6605,7 +6605,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>335</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>335</v>
       </c>
@@ -6669,7 +6669,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>360</v>
       </c>
@@ -6701,7 +6701,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>360</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>360</v>
       </c>
@@ -6765,7 +6765,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>360</v>
       </c>
@@ -6797,7 +6797,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>360</v>
       </c>
@@ -6829,7 +6829,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>360</v>
       </c>
@@ -6861,7 +6861,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165"/>
       <c r="B165"/>
       <c r="C165"/>
@@ -6873,7 +6873,7 @@
       <c r="I165"/>
       <c r="J165"/>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166"/>
       <c r="B166"/>
       <c r="C166"/>
@@ -6885,7 +6885,7 @@
       <c r="I166"/>
       <c r="J166"/>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F167"/>
     </row>
   </sheetData>
